--- a/data/chapter16_tidyr_dpylr.xlsx
+++ b/data/chapter16_tidyr_dpylr.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kyowapharma-my.sharepoint.com/personal/araya-t_kyowayakuhin_co_jp/Documents/R_scripts/R入門/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{A88526A0-76D3-402E-8859-87A7E02FE9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C5C68A9-E359-4A44-BF43-5C5DA979515C}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E75B43E-1070-4D13-AFEF-A174610686CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10152" windowHeight="12960" activeTab="1" xr2:uid="{B01627E0-51A8-48EA-B3BA-D7B1A4413057}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="16440" activeTab="1" xr2:uid="{B01627E0-51A8-48EA-B3BA-D7B1A4413057}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -795,14 +790,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -840,7 +831,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -946,7 +937,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1088,7 +1079,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1097,12 +1088,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54AFC9DB-F57A-44C4-AC70-BBAAC9F00D85}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="30.3984375" customWidth="1"/>
+    <col min="1" max="2" width="30.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1110,7 +1101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1118,7 +1109,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1126,7 +1117,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1134,7 +1125,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1142,7 +1133,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1150,7 +1141,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1158,7 +1149,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1166,7 +1157,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1174,7 +1165,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1182,7 +1173,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1190,7 +1181,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1201,18 +1192,19 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCFD1124-9198-4EC4-9DF6-31CF51EF444D}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="24.69921875" customWidth="1"/>
+    <col min="1" max="2" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1220,7 +1212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1228,7 +1220,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1236,7 +1228,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1244,7 +1236,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -1252,7 +1244,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1260,7 +1252,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1268,7 +1260,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -1276,7 +1268,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1284,7 +1276,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1292,7 +1284,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1300,7 +1292,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1308,7 +1300,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1316,7 +1308,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -1324,7 +1316,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1332,7 +1324,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1340,7 +1332,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1348,7 +1340,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1356,7 +1348,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1367,18 +1359,19 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B7B7709-C7E5-4579-9B71-99647D578CDF}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="35.19921875" customWidth="1"/>
+    <col min="1" max="2" width="35.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1386,7 +1379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>54</v>
       </c>
@@ -1394,7 +1387,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -1402,7 +1395,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>55</v>
       </c>
@@ -1410,7 +1403,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -1418,7 +1411,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -1426,7 +1419,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -1434,7 +1427,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -1442,7 +1435,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -1450,7 +1443,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>71</v>
       </c>
@@ -1458,7 +1451,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>72</v>
       </c>
@@ -1466,7 +1459,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>74</v>
       </c>
@@ -1477,5 +1470,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>